--- a/docs/planning/2026-07-08-OMF-MES-개발-WBS.xlsx
+++ b/docs/planning/2026-07-08-OMF-MES-개발-WBS.xlsx
@@ -655,7 +655,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>v0.1 — 작성 중 (초안). 일정 앵커(UI/UX 마감·개발 완료·현장 4주) 외 일자는 추정치이며 §8 결정 후 v1.0에서 확정</t>
+          <t>v0.2 — 작성 중 · §8 결정 3건 종결(2026-07-10, 기술스택·배포모델 결정서 v0.2). 일정 앵커(UI/UX 마감·개발 완료·현장 4주) 외 일자는 추정치이며 잔여 §8 결정(#4~#8) 후 v1.0에서 확정</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>FE/BE/DB/인프라 스택 + 현장 온프렘 vs 클라우드(오프라인 내성·백업 5~10년 고려)</t>
+          <t>✅확정(2026-07-10) — 결정 15·16: PostgreSQL · TypeScript(NestJS) · React 코드 1벌(관리 웹/POP Electron 앱/모바일 Capacitor Android 앱) · Ubuntu+Docker Compose · 공장 내부 서버 2대(웜 스탠바이)+백업 NAS · 오프라인 설치 패키지 배포</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>기술 스택 결정서</t>
+          <t>기술스택·배포모델 결정서 v0.2</t>
         </is>
       </c>
       <c r="J3" s="6" t="inlineStr"/>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="L3" s="6" t="inlineStr">
         <is>
-          <t>대기</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
-          <t>전 문서에 미확정 — 최우선</t>
+          <t>2026-07-10 CTO 확정 (결정 15~19)</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>폼팩터 3종 공통: 관리 Desktop / POP 현장(큰 터치·한베 전환·오프라인 표시) / 모바일 스캐너</t>
+          <t>폼팩터 3종 공통: 관리 Desktop 웹 / POP 현장 — 산업용 패널 PC·터치 중심·Electron 앱(큰 터치·한베 전환·오프라인/미동기 표시) / 모바일 스캐너 — Capacitor Android 앱 (결정 16)</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>LOT 3종(자재 2단계·생산 선발행·제품) + 작업지시 전 유형 + 상위지시 nullable 참조(0..1:N) 공통 스키마</t>
+          <t>LOT 3종(자재 2단계·생산 선발행·제품) + 작업지시 전 유형 + 상위지시 nullable 참조(0..1:N) 공통 스키마 + W/O 발행 시 일괄 발번(결정 17)</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>사전발행→활성→폐번(P3) 라이프사이클, 라벨 8종 포맷, 재출력 정책(정본=시스템 수량)</t>
+          <t>사전발행→활성→폐번(P3) 라이프사이클, 라벨 8종 포맷, 재출력 정책(정본=시스템 수량) + 서버 렌더링(한/베 폰트)·W/O 단위 선발행·POP 선배포 API(결정 17·18)</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="M20" s="10" t="inlineStr">
         <is>
-          <t>트랙 H 라벨 셋팅 프로그램과 연동</t>
+          <t>인쇄는 POP 앱 내장(결정 18) — 4.6과 연동</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="D49" s="15" t="inlineStr">
         <is>
-          <t>발주(W2)·개발용 실기 1세트 선확보(W3 목표)·전 수량 현장 도착(W7 목표)</t>
+          <t>발주(W2 — 서버 2대·백업 NAS·N100 패널 PC 포함, 결정 15·16)·개발용 실기 1세트 선확보(W3 목표)·전 수량 현장 도착(W7 목표)</t>
         </is>
       </c>
       <c r="E49" s="15" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="K49" s="15" t="inlineStr">
         <is>
-          <t>베트남 현지 구매(모바일)·TTP-247 EoL 확인·E2/E7 대기·OA 재사용 실사</t>
+          <t>베트남 현지 구매(모바일 — OS=Android 확정)·TTP-247 EoL 확인·E2/E7 대기·OA 재사용 실사·NAS 위치=고객 선택 대기</t>
         </is>
       </c>
       <c r="L49" s="15" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>H 라벨 셋팅 프로그램·스캐너 입력</t>
+          <t>H POP 앱 인쇄·스캐너 입력</t>
         </is>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>라벨 8종 출력 프로그램(모듈 D PC)·스캔 플로우(출고 QR 양방향·오투입·적치 검증·Matching)·실기 검증(W6~7)</t>
+          <t>라벨 8종 인쇄(서버 렌더링 이미지 — POP 앱 내장, 구 라벨 셋팅 프로그램 대체, 결정 18)·스캔 플로우(출고 QR 양방향·오투입·적치 검증·Matching)·실기 검증(W6~7: N100 Electron·터치·무선랜)</t>
         </is>
       </c>
       <c r="E50" s="15" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="D51" s="15" t="inlineStr">
         <is>
-          <t>POP 로컬 버퍼링+복구 시 자동 동기화 (아키텍처는 P0에서 선결정 — 후부착 불가)</t>
+          <t>POP 로컬 버퍼링+복구 시 자동 동기화 — ✅아키텍처 확정(결정 17): 최소 운영 시나리오 2건(① W/O 선배포로 생산 계속 ② 자재 입·출고 단일 단말 스캔) + outbox·멱등 키·시각 분리. 그 외 기능 오프라인 미지원</t>
         </is>
       </c>
       <c r="E51" s="15" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="M51" s="15" t="inlineStr">
         <is>
-          <t>QA #32</t>
+          <t>QA #32 · 결정 17</t>
         </is>
       </c>
     </row>
@@ -4026,17 +4026,17 @@
       </c>
       <c r="C54" s="15" t="inlineStr">
         <is>
-          <t>AI 문서분석 2종</t>
+          <t>문서 입력 자동화 2종 (구 트랙 AI — 폐지)</t>
         </is>
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t>거래명세서 촬영→자동 입하 등록(QA #29)·출하지시서 엑셀 자동 import — 확정분. 추가 AI 기능은 §8-3 결정 후</t>
+          <t>거래명세서 촬영→온프레 OCR 입하 프리필(QA #29, 수기 폴백)·출하지시서 결정론적 엑셀 파서 import — ✅AI Agent 전면 제외(결정 19), D01·D04 도메인 기능으로 수행</t>
         </is>
       </c>
       <c r="E54" s="15" t="inlineStr">
         <is>
-          <t>AI 에이전트</t>
+          <t>D01·D04 레인</t>
         </is>
       </c>
       <c r="F54" s="15" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="K54" s="15" t="inlineStr">
         <is>
-          <t>§8-3 AI 1차 범위 결정</t>
+          <t>✅결정 19 종결 — 잔여: OCR 엔진 선정(온프레)·RAG 포함 여부</t>
         </is>
       </c>
       <c r="L54" s="15" t="inlineStr">
@@ -5014,7 +5014,6 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
       <c r="B2" s="22" t="inlineStr">
         <is>
           <t>(음영 = 해당 주차 수행)</t>
@@ -6872,7 +6871,7 @@
       </c>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t>모바일=베트남 현지 구매 필수(기종 미정), TTP-247 EoL 가능성, 수량은 E2·E7 대기</t>
+          <t>모바일=베트남 현지 구매 필수(기종 미정·OS=Android 확정), TTP-247 EoL 가능성, 서버 2대·NAS·N100 패널 PC 추가(결정 15·16), 수량은 E2·E7 대기</t>
         </is>
       </c>
       <c r="E4" s="21" t="inlineStr">
@@ -7229,12 +7228,12 @@
       </c>
       <c r="C2" s="13" t="inlineStr">
         <is>
-          <t>전 문서 미확정. 유일한 참조=UNIMES 스택(Windows Server+IIS+MS-SQL — 비젠트로 것). Agent coding 생산성·다국어·오프라인 내성 기준으로 즉시 결정</t>
+          <t>✅종결(2026-07-10) — 결정 16: PostgreSQL · TypeScript(NestJS) · React 코드 1벌(관리 웹/POP Electron 앱/모바일 Capacitor Android 앱) · Ubuntu+Docker Compose · 오프라인 설치 패키지 배포(고객사 서버 자동 배포 금지)</t>
         </is>
       </c>
       <c r="D2" s="13" t="inlineStr">
         <is>
-          <t>0.1 (07-10까지)</t>
+          <t>✅종결 — 결정서 v0.2</t>
         </is>
       </c>
     </row>
@@ -7251,12 +7250,12 @@
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>현장 온프레미스 서버 vs 클라우드+현장 게이트웨이 — 네트워크 불안정(REQ-OA-0005)·백업 5~10년(REQ-PR-0018)·베트남 현장 조건</t>
+          <t>✅종결(2026-07-10) — 결정 15: 고객사 공장 내부 설치형 서버(웜 스탠바이 이중화) + 백업 NAS · 인터넷=설치·유지보수 시만 일시 보장(C11) (잔여: NAS 위치·격리=고객 선택 대기)</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>0.1 (07-10까지)</t>
+          <t>✅종결 — 결정서 v0.2</t>
         </is>
       </c>
     </row>
@@ -7273,12 +7272,12 @@
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>확정분(문서분석 2종) 외 NLQ/일일 브리핑/FEFO 제안 등 코파일럿 포함 여부 — 기획서 차별화 축이나 요구사항 47건에는 없음</t>
+          <t>✅종결(2026-07-10) — 결정 19: AI Agent 전면 제외 · 거래명세서=온프레 OCR·출하지시=엑셀 파서(D01·D04 이관) · NLQ/브리핑/FEFO=OMF-AI 이연 (잔여: OCR 엔진 선정·RAG 포함 여부)</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>W2 내</t>
+          <t>✅종결 — 결정서 v0.2</t>
         </is>
       </c>
     </row>

--- a/docs/planning/2026-07-08-OMF-MES-개발-WBS.xlsx
+++ b/docs/planning/2026-07-08-OMF-MES-개발-WBS.xlsx
@@ -655,7 +655,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>v0.2 — 작성 중 · §8 결정 3건 종결(2026-07-10, 기술스택·배포모델 결정서 v0.2). 일정 앵커(UI/UX 마감·개발 완료·현장 4주) 외 일자는 추정치이며 잔여 §8 결정(#4~#8) 후 v1.0에서 확정</t>
+          <t>v0.3 — 작성 중 · §8 결정 3건 종결(2026-07-10, 기술스택·배포모델 결정서 v0.2) · 정본 md 일정 동기화(2026-07-13: UI/UX 마감 07-17·수출 준비 W9). 일정 앵커(UI/UX 마감·개발 완료·현장 4주) 외 일자는 추정치이며 잔여 §8 결정(#4~#8) 후 v1.0에서 확정</t>
         </is>
       </c>
     </row>
